--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>764.4865192181571</v>
+        <v>655.109465858917</v>
       </c>
       <c r="C2">
-        <v>418.4496975564105</v>
+        <v>397.054121568658</v>
       </c>
       <c r="D2">
-        <v>328.1660104757132</v>
+        <v>318.8255074794104</v>
       </c>
       <c r="E2">
-        <v>286.8234418175787</v>
+        <v>286.3670428011163</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>871.0289635510998</v>
+        <v>738.8844656338746</v>
       </c>
       <c r="C3">
-        <v>484.8770979451076</v>
+        <v>455.0914956106583</v>
       </c>
       <c r="D3">
-        <v>381.9381445283124</v>
+        <v>369.9449567063604</v>
       </c>
       <c r="E3">
-        <v>337.539720704105</v>
+        <v>336.5419097197253</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>854.9972987449366</v>
+        <v>718.6452675061884</v>
       </c>
       <c r="C4">
-        <v>474.3442698171265</v>
+        <v>441.2720317847247</v>
       </c>
       <c r="D4">
-        <v>372.6505164845577</v>
+        <v>357.2723881202125</v>
       </c>
       <c r="E4">
-        <v>329.2111233072053</v>
+        <v>325.002861869018</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>569.1313722990498</v>
+        <v>486.252025593674</v>
       </c>
       <c r="C5">
-        <v>327.3027464151228</v>
+        <v>304.0158562394433</v>
       </c>
       <c r="D5">
-        <v>254.1870649260763</v>
+        <v>243.4109382279339</v>
       </c>
       <c r="E5">
-        <v>226.7758417148181</v>
+        <v>223.5045150867777</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>424.4418026900117</v>
+        <v>422.9326213845731</v>
       </c>
       <c r="C6">
-        <v>268.1912820599164</v>
+        <v>265.6878165860058</v>
       </c>
       <c r="D6">
-        <v>221.4050858835137</v>
+        <v>215.4797378999488</v>
       </c>
       <c r="E6">
-        <v>196.612059074901</v>
+        <v>195.3949058874323</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>48.45512858836758</v>
+        <v>42.33881511500822</v>
       </c>
       <c r="C7">
-        <v>29.41818687951267</v>
+        <v>27.52468066638528</v>
       </c>
       <c r="D7">
-        <v>23.80803174869664</v>
+        <v>22.96936741620498</v>
       </c>
       <c r="E7">
-        <v>20.86458629994829</v>
+        <v>20.75432721078036</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1685.980398600369</v>
+        <v>2399.913128486762</v>
       </c>
       <c r="C8">
-        <v>1234.037006739788</v>
+        <v>1456.232203551763</v>
       </c>
       <c r="D8">
-        <v>1108.79858268779</v>
+        <v>1199.41802773978</v>
       </c>
       <c r="E8">
-        <v>1076.224503246964</v>
+        <v>1090.646068279826</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>584.3834546921158</v>
+        <v>558.1283079292006</v>
       </c>
       <c r="C9">
-        <v>375.1745696129718</v>
+        <v>365.7315903097206</v>
       </c>
       <c r="D9">
-        <v>313.9960287543362</v>
+        <v>306.7714043899269</v>
       </c>
       <c r="E9">
-        <v>281.4538724956348</v>
+        <v>280.6582477492913</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>304.4251458185302</v>
+        <v>251.0414618114544</v>
       </c>
       <c r="C10">
-        <v>174.8934120558238</v>
+        <v>159.4885539017561</v>
       </c>
       <c r="D10">
-        <v>139.4316336290295</v>
+        <v>132.832166470427</v>
       </c>
       <c r="E10">
-        <v>120.7346305157058</v>
+        <v>118.8077440582913</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>55.69333481839095</v>
+        <v>45.75388666049335</v>
       </c>
       <c r="C11">
-        <v>30.38056036881716</v>
+        <v>27.68345644684883</v>
       </c>
       <c r="D11">
-        <v>23.99403721049302</v>
+        <v>22.85243694743759</v>
       </c>
       <c r="E11">
-        <v>22.41179303283225</v>
+        <v>22.05293992996112</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>117.7167208127807</v>
+        <v>96.06209854889983</v>
       </c>
       <c r="C12">
-        <v>75.71151988413908</v>
+        <v>68.82690635307382</v>
       </c>
       <c r="D12">
-        <v>62.53373256970758</v>
+        <v>59.54072938600125</v>
       </c>
       <c r="E12">
-        <v>53.55384386115224</v>
+        <v>52.69241524504732</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>163.5233485432104</v>
+        <v>134.8943332346496</v>
       </c>
       <c r="C13">
-        <v>95.50545873374278</v>
+        <v>87.10512377289452</v>
       </c>
       <c r="D13">
-        <v>77.76696643377902</v>
+        <v>74.07527741186301</v>
       </c>
       <c r="E13">
-        <v>68.24637133273622</v>
+        <v>67.155325355434</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>486.252025593674</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>304.0158562394433</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>243.4109382279339</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>223.5045150867777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2399.913128486762</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1456.232203551763</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1199.41802773978</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1090.646068279826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>251.0414618114544</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>159.4885539017561</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>132.832166470427</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>118.8077440582913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>45.75388666049335</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>27.68345644684883</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>22.85243694743759</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>22.05293992996112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>134.8943332346496</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>87.10512377289452</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>74.07527741186301</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>67.155325355434</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
